--- a/plots/plots.xlsx
+++ b/plots/plots.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman_Melnyk1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman_Melnyk1\IdeaProjects\battery-model\plots\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D8650C-948E-41EA-929E-F0AC7F36A462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097AD4E3-40DE-45EB-BE27-0E09B319779E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="з1-3" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
   <si>
     <t>[1:3]</t>
   </si>
@@ -1167,6 +1167,537 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-3E49-421E-B895-12A474E12F09}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'з1-3'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>МНК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'з1-3'!$E$4:$E$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'з1-3'!$F$4:$F$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>52.29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>52.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>52.34</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>52.37</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>52.39</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>52.42</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>52.45</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52.47</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>52.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>52.52</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>52.55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>52.57</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>52.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>52.62</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>52.65</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>52.67</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>52.7</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>52.72</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>52.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>52.77</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>52.79</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>52.82</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>52.84</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>52.86</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>52.88</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>52.91</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>52.93</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>52.95</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>52.97</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>52.99</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>53.01</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>53.03</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>53.05</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.07</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>53.09</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>53.11</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>53.13</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>53.15</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>53.17</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>53.18</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>53.2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>53.22</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>53.23</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>53.25</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>53.27</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>53.28</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>53.3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>53.31</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>53.32</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>53.34</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>53.35</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>53.36</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53.37</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53.39</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>53.4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>53.41</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>53.42</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>53.43</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>53.43</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>53.44</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>53.45</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>53.46</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>53.46</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>53.47</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>53.48</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>53.48</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>53.5</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>53.5</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>53.5</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>53.5</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>53.5</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>53.5</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>53.48</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0681-498A-8635-F802FE2BBB79}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4246,6 +4777,537 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'з9-11'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>МНК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'з9-11'!$E$4:$E$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'з9-11'!$F$4:$F$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>53.03</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.04</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.05</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53.06</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.07</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53.08</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>53.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>53.11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>53.12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>53.13</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53.14</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>53.16</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>53.17</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>53.18</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>53.19</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>53.21</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>53.22</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>53.23</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>53.24</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>53.26</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>53.27</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>53.28</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>53.3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53.31</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>53.33</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>53.34</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53.35</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>53.37</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>53.38</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>53.4</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>53.41</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>53.43</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>53.44</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.46</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>53.47</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>53.51</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>53.52</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>53.54</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>53.55</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>53.57</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>53.59</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>53.6</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>53.62</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>53.64</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>53.66</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>53.67</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>53.69</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>53.71</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>53.73</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>53.74</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>53.76</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53.78</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>53.82</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>53.84</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>53.86</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>53.88</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>53.9</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>53.92</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>53.94</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>53.96</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>53.98</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>54.02</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>54.04</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>54.06</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>54.09</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>54.11</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>54.13</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>54.15</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>54.17</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>54.2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>54.22</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>54.24</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>54.27</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>54.29</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>54.32</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>54.34</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>54.36</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-13FC-4276-B56C-2E27C68B5C67}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -7306,6 +8368,537 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-BB6C-41A6-BDD5-3DEFBA6B7CFB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'з19-21'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>МНК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'з19-21'!$F$4:$F$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'з19-21'!$G$4:$G$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>53.31</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.33</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53.35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.36</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53.37</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>53.39</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>53.4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>53.41</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>53.42</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53.44</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>53.45</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>53.47</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>53.48</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>53.49</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>53.51</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>53.52</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>53.53</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>53.55</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>53.56</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>53.58</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>53.59</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>53.61</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53.62</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>53.64</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>53.65</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53.66</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>53.68</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>53.69</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>53.71</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>53.73</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>53.74</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>53.76</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.77</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>53.79</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>53.82</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>53.84</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>53.85</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>53.87</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>53.88</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>53.9</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>53.92</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>53.93</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>53.95</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>53.97</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>53.99</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>54.02</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>54.04</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>54.06</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>54.07</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>54.09</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54.11</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54.13</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>54.15</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>54.17</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>54.18</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>54.2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>54.22</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>54.24</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>54.26</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>54.28</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>54.3</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>54.32</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>54.34</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>54.36</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>54.38</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>54.4</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>54.42</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>54.44</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>54.46</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>54.48</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>54.5</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>54.52</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>54.54</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>54.57</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>54.59</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>54.61</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>54.63</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BD8B-41BF-AC80-CF6B77426EE5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10185,6 +11778,537 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-279A-4E89-9CEE-D607677FD3CF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'з29-31'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>МНК</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'з29-31'!$F$4:$F$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'з29-31'!$G$4:$G$83</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>53.52</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>53.54</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>53.55</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>53.56</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>53.57</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53.59</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>53.6</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>53.61</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>53.63</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>53.64</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>53.65</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>53.67</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>53.68</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>53.69</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>53.71</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>53.72</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>53.73</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>53.75</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>53.76</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>53.78</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>53.79</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>53.8</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>53.82</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>53.83</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>53.85</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>53.86</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>53.88</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>53.89</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>53.91</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>53.92</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>53.94</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>53.95</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>53.97</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>53.98</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>54.01</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>54.03</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>54.04</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>54.06</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>54.07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>54.09</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>54.11</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>54.12</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>54.14</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>54.15</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>54.17</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>54.19</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>54.2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>54.22</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>54.24</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>54.25</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>54.27</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>54.29</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54.31</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>54.32</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>54.34</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>54.36</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>54.37</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>54.39</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>54.41</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>54.43</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>54.45</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>54.46</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>54.48</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>54.5</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>54.52</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>54.54</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>54.56</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>54.58</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>54.59</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>54.61</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>54.63</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>54.65</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>54.67</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>54.69</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>54.71</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>54.73</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>54.75</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>54.77</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>54.79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4486-4BD8-9C1C-F92CA8B28F71}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -16930,6 +19054,12 @@
       <c r="C4">
         <v>51.999927</v>
       </c>
+      <c r="E4">
+        <v>0.2</v>
+      </c>
+      <c r="F4">
+        <v>52.29</v>
+      </c>
       <c r="I4">
         <v>0.2</v>
       </c>
@@ -16944,6 +19074,12 @@
       <c r="C5">
         <v>52.096609999999998</v>
       </c>
+      <c r="E5">
+        <v>0.21</v>
+      </c>
+      <c r="F5">
+        <v>52.32</v>
+      </c>
       <c r="I5">
         <v>0.21</v>
       </c>
@@ -16958,6 +19094,12 @@
       <c r="C6">
         <v>52.183436</v>
       </c>
+      <c r="E6">
+        <v>0.22</v>
+      </c>
+      <c r="F6">
+        <v>52.34</v>
+      </c>
       <c r="I6">
         <v>0.22</v>
       </c>
@@ -16972,6 +19114,12 @@
       <c r="C7">
         <v>52.261214000000002</v>
       </c>
+      <c r="E7">
+        <v>0.23</v>
+      </c>
+      <c r="F7">
+        <v>52.37</v>
+      </c>
       <c r="I7">
         <v>0.23</v>
       </c>
@@ -16986,6 +19134,12 @@
       <c r="C8">
         <v>52.330714</v>
       </c>
+      <c r="E8">
+        <v>0.24</v>
+      </c>
+      <c r="F8">
+        <v>52.39</v>
+      </c>
       <c r="I8">
         <v>0.24</v>
       </c>
@@ -17000,6 +19154,12 @@
       <c r="C9">
         <v>52.392665999999998</v>
       </c>
+      <c r="E9">
+        <v>0.25</v>
+      </c>
+      <c r="F9">
+        <v>52.42</v>
+      </c>
       <c r="I9">
         <v>0.25</v>
       </c>
@@ -17014,6 +19174,12 @@
       <c r="C10">
         <v>52.447763000000002</v>
       </c>
+      <c r="E10">
+        <v>0.26</v>
+      </c>
+      <c r="F10">
+        <v>52.45</v>
+      </c>
       <c r="I10">
         <v>0.26</v>
       </c>
@@ -17028,6 +19194,12 @@
       <c r="C11">
         <v>52.496661000000003</v>
       </c>
+      <c r="E11">
+        <v>0.27</v>
+      </c>
+      <c r="F11">
+        <v>52.47</v>
+      </c>
       <c r="I11">
         <v>0.27</v>
       </c>
@@ -17042,6 +19214,12 @@
       <c r="C12">
         <v>52.53998</v>
       </c>
+      <c r="E12">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F12">
+        <v>52.5</v>
+      </c>
       <c r="I12">
         <v>0.28000000000000003</v>
       </c>
@@ -17056,6 +19234,12 @@
       <c r="C13">
         <v>52.578302999999998</v>
       </c>
+      <c r="E13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F13">
+        <v>52.52</v>
+      </c>
       <c r="I13">
         <v>0.28999999999999998</v>
       </c>
@@ -17070,6 +19254,12 @@
       <c r="C14">
         <v>52.612181</v>
       </c>
+      <c r="E14">
+        <v>0.3</v>
+      </c>
+      <c r="F14">
+        <v>52.55</v>
+      </c>
       <c r="I14">
         <v>0.3</v>
       </c>
@@ -17084,6 +19274,12 @@
       <c r="C15">
         <v>52.642128</v>
       </c>
+      <c r="E15">
+        <v>0.31</v>
+      </c>
+      <c r="F15">
+        <v>52.57</v>
+      </c>
       <c r="I15">
         <v>0.31</v>
       </c>
@@ -17098,6 +19294,12 @@
       <c r="C16">
         <v>52.66863</v>
       </c>
+      <c r="E16">
+        <v>0.32</v>
+      </c>
+      <c r="F16">
+        <v>52.6</v>
+      </c>
       <c r="I16">
         <v>0.32</v>
       </c>
@@ -17112,6 +19314,12 @@
       <c r="C17">
         <v>52.692138</v>
       </c>
+      <c r="E17">
+        <v>0.33</v>
+      </c>
+      <c r="F17">
+        <v>52.62</v>
+      </c>
       <c r="I17">
         <v>0.33</v>
       </c>
@@ -17126,6 +19334,12 @@
       <c r="C18">
         <v>52.713070999999999</v>
       </c>
+      <c r="E18">
+        <v>0.34</v>
+      </c>
+      <c r="F18">
+        <v>52.65</v>
+      </c>
       <c r="I18">
         <v>0.34</v>
       </c>
@@ -17140,6 +19354,12 @@
       <c r="C19">
         <v>52.731822000000001</v>
       </c>
+      <c r="E19">
+        <v>0.35</v>
+      </c>
+      <c r="F19">
+        <v>52.67</v>
+      </c>
       <c r="I19">
         <v>0.35</v>
       </c>
@@ -17154,6 +19374,12 @@
       <c r="C20">
         <v>52.748752000000003</v>
       </c>
+      <c r="E20">
+        <v>0.36</v>
+      </c>
+      <c r="F20">
+        <v>52.7</v>
+      </c>
       <c r="I20">
         <v>0.36</v>
       </c>
@@ -17168,6 +19394,12 @@
       <c r="C21">
         <v>52.764194000000003</v>
       </c>
+      <c r="E21">
+        <v>0.37</v>
+      </c>
+      <c r="F21">
+        <v>52.72</v>
+      </c>
       <c r="I21">
         <v>0.37</v>
       </c>
@@ -17182,6 +19414,12 @@
       <c r="C22">
         <v>52.778454000000004</v>
       </c>
+      <c r="E22">
+        <v>0.38</v>
+      </c>
+      <c r="F22">
+        <v>52.75</v>
+      </c>
       <c r="I22">
         <v>0.38</v>
       </c>
@@ -17196,6 +19434,12 @@
       <c r="C23">
         <v>52.791812</v>
       </c>
+      <c r="E23">
+        <v>0.39</v>
+      </c>
+      <c r="F23">
+        <v>52.77</v>
+      </c>
       <c r="I23">
         <v>0.39</v>
       </c>
@@ -17210,6 +19454,12 @@
       <c r="C24">
         <v>52.804521000000001</v>
       </c>
+      <c r="E24">
+        <v>0.4</v>
+      </c>
+      <c r="F24">
+        <v>52.79</v>
+      </c>
       <c r="I24">
         <v>0.4</v>
       </c>
@@ -17224,6 +19474,12 @@
       <c r="C25">
         <v>52.816809999999997</v>
       </c>
+      <c r="E25">
+        <v>0.41</v>
+      </c>
+      <c r="F25">
+        <v>52.82</v>
+      </c>
       <c r="I25">
         <v>0.41</v>
       </c>
@@ -17238,6 +19494,12 @@
       <c r="C26">
         <v>52.828885999999997</v>
       </c>
+      <c r="E26">
+        <v>0.42</v>
+      </c>
+      <c r="F26">
+        <v>52.84</v>
+      </c>
       <c r="I26">
         <v>0.42</v>
       </c>
@@ -17252,6 +19514,12 @@
       <c r="C27">
         <v>52.840929000000003</v>
       </c>
+      <c r="E27">
+        <v>0.43</v>
+      </c>
+      <c r="F27">
+        <v>52.86</v>
+      </c>
       <c r="I27">
         <v>0.43</v>
       </c>
@@ -17266,6 +19534,12 @@
       <c r="C28">
         <v>52.853101000000002</v>
       </c>
+      <c r="E28">
+        <v>0.44</v>
+      </c>
+      <c r="F28">
+        <v>52.88</v>
+      </c>
       <c r="I28">
         <v>0.44</v>
       </c>
@@ -17280,6 +19554,12 @@
       <c r="C29">
         <v>52.865540000000003</v>
       </c>
+      <c r="E29">
+        <v>0.45</v>
+      </c>
+      <c r="F29">
+        <v>52.91</v>
+      </c>
       <c r="I29">
         <v>0.45</v>
       </c>
@@ -17294,6 +19574,12 @@
       <c r="C30">
         <v>52.878365000000002</v>
       </c>
+      <c r="E30">
+        <v>0.46</v>
+      </c>
+      <c r="F30">
+        <v>52.93</v>
+      </c>
       <c r="I30">
         <v>0.46</v>
       </c>
@@ -17308,6 +19594,12 @@
       <c r="C31">
         <v>52.891674999999999</v>
       </c>
+      <c r="E31">
+        <v>0.47</v>
+      </c>
+      <c r="F31">
+        <v>52.95</v>
+      </c>
       <c r="I31">
         <v>0.47</v>
       </c>
@@ -17322,6 +19614,12 @@
       <c r="C32">
         <v>52.905549999999998</v>
       </c>
+      <c r="E32">
+        <v>0.48</v>
+      </c>
+      <c r="F32">
+        <v>52.97</v>
+      </c>
       <c r="I32">
         <v>0.48</v>
       </c>
@@ -17336,6 +19634,12 @@
       <c r="C33">
         <v>52.935234000000001</v>
       </c>
+      <c r="E33">
+        <v>0.49</v>
+      </c>
+      <c r="F33">
+        <v>52.99</v>
+      </c>
       <c r="I33">
         <v>0.49</v>
       </c>
@@ -17350,6 +19654,12 @@
       <c r="C34">
         <v>53.003086000000003</v>
       </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>53.01</v>
+      </c>
       <c r="I34">
         <v>0.5</v>
       </c>
@@ -17364,6 +19674,12 @@
       <c r="C35">
         <v>53.061146999999998</v>
       </c>
+      <c r="E35">
+        <v>0.51</v>
+      </c>
+      <c r="F35">
+        <v>53.03</v>
+      </c>
       <c r="I35">
         <v>0.51</v>
       </c>
@@ -17378,6 +19694,12 @@
       <c r="C36">
         <v>53.081664000000004</v>
       </c>
+      <c r="E36">
+        <v>0.52</v>
+      </c>
+      <c r="F36">
+        <v>53.05</v>
+      </c>
       <c r="I36">
         <v>0.52</v>
       </c>
@@ -17392,6 +19714,12 @@
       <c r="C37">
         <v>53.145792999999998</v>
       </c>
+      <c r="E37">
+        <v>0.53</v>
+      </c>
+      <c r="F37">
+        <v>53.07</v>
+      </c>
       <c r="I37">
         <v>0.53</v>
       </c>
@@ -17406,6 +19734,12 @@
       <c r="C38">
         <v>53.167762000000003</v>
       </c>
+      <c r="E38">
+        <v>0.54</v>
+      </c>
+      <c r="F38">
+        <v>53.09</v>
+      </c>
       <c r="I38">
         <v>0.54</v>
       </c>
@@ -17420,6 +19754,12 @@
       <c r="C39">
         <v>53.189880000000002</v>
       </c>
+      <c r="E39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F39">
+        <v>53.11</v>
+      </c>
       <c r="I39">
         <v>0.55000000000000004</v>
       </c>
@@ -17434,6 +19774,12 @@
       <c r="C40">
         <v>53.212048000000003</v>
       </c>
+      <c r="E40">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F40">
+        <v>53.13</v>
+      </c>
       <c r="I40">
         <v>0.56000000000000005</v>
       </c>
@@ -17448,6 +19794,12 @@
       <c r="C41">
         <v>53.234167999999997</v>
       </c>
+      <c r="E41">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F41">
+        <v>53.15</v>
+      </c>
       <c r="I41">
         <v>0.56999999999999995</v>
       </c>
@@ -17462,6 +19814,12 @@
       <c r="C42">
         <v>53.256137000000003</v>
       </c>
+      <c r="E42">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F42">
+        <v>53.17</v>
+      </c>
       <c r="I42">
         <v>0.57999999999999996</v>
       </c>
@@ -17476,6 +19834,12 @@
       <c r="C43">
         <v>53.277850000000001</v>
       </c>
+      <c r="E43">
+        <v>0.59</v>
+      </c>
+      <c r="F43">
+        <v>53.18</v>
+      </c>
       <c r="I43">
         <v>0.59</v>
       </c>
@@ -17490,6 +19854,12 @@
       <c r="C44">
         <v>53.299202000000001</v>
       </c>
+      <c r="E44">
+        <v>0.6</v>
+      </c>
+      <c r="F44">
+        <v>53.2</v>
+      </c>
       <c r="I44">
         <v>0.6</v>
       </c>
@@ -17504,6 +19874,12 @@
       <c r="C45">
         <v>53.320087999999998</v>
       </c>
+      <c r="E45">
+        <v>0.61</v>
+      </c>
+      <c r="F45">
+        <v>53.22</v>
+      </c>
       <c r="I45">
         <v>0.61</v>
       </c>
@@ -17518,6 +19894,12 @@
       <c r="C46">
         <v>53.340401999999997</v>
       </c>
+      <c r="E46">
+        <v>0.62</v>
+      </c>
+      <c r="F46">
+        <v>53.23</v>
+      </c>
       <c r="I46">
         <v>0.62</v>
       </c>
@@ -17532,6 +19914,12 @@
       <c r="C47">
         <v>53.360042999999997</v>
       </c>
+      <c r="E47">
+        <v>0.63</v>
+      </c>
+      <c r="F47">
+        <v>53.25</v>
+      </c>
       <c r="I47">
         <v>0.63</v>
       </c>
@@ -17546,6 +19934,12 @@
       <c r="C48">
         <v>53.378909</v>
       </c>
+      <c r="E48">
+        <v>0.64</v>
+      </c>
+      <c r="F48">
+        <v>53.27</v>
+      </c>
       <c r="I48">
         <v>0.64</v>
       </c>
@@ -17560,6 +19954,12 @@
       <c r="C49">
         <v>53.396903999999999</v>
       </c>
+      <c r="E49">
+        <v>0.65</v>
+      </c>
+      <c r="F49">
+        <v>53.28</v>
+      </c>
       <c r="I49">
         <v>0.65</v>
       </c>
@@ -17574,6 +19974,12 @@
       <c r="C50">
         <v>53.413936</v>
       </c>
+      <c r="E50">
+        <v>0.66</v>
+      </c>
+      <c r="F50">
+        <v>53.3</v>
+      </c>
       <c r="I50">
         <v>0.66</v>
       </c>
@@ -17588,6 +19994,12 @@
       <c r="C51">
         <v>53.429918000000001</v>
       </c>
+      <c r="E51">
+        <v>0.67</v>
+      </c>
+      <c r="F51">
+        <v>53.31</v>
+      </c>
       <c r="I51">
         <v>0.67</v>
       </c>
@@ -17602,6 +20014,12 @@
       <c r="C52">
         <v>53.444768000000003</v>
       </c>
+      <c r="E52">
+        <v>0.68</v>
+      </c>
+      <c r="F52">
+        <v>53.32</v>
+      </c>
       <c r="I52">
         <v>0.68</v>
       </c>
@@ -17616,6 +20034,12 @@
       <c r="C53">
         <v>53.458412000000003</v>
       </c>
+      <c r="E53">
+        <v>0.69</v>
+      </c>
+      <c r="F53">
+        <v>53.34</v>
+      </c>
       <c r="I53">
         <v>0.69</v>
       </c>
@@ -17630,6 +20054,12 @@
       <c r="C54">
         <v>53.470784000000002</v>
       </c>
+      <c r="E54">
+        <v>0.7</v>
+      </c>
+      <c r="F54">
+        <v>53.35</v>
+      </c>
       <c r="I54">
         <v>0.7</v>
       </c>
@@ -17644,6 +20074,12 @@
       <c r="C55">
         <v>53.481828</v>
       </c>
+      <c r="E55">
+        <v>0.71</v>
+      </c>
+      <c r="F55">
+        <v>53.36</v>
+      </c>
       <c r="I55">
         <v>0.71</v>
       </c>
@@ -17658,6 +20094,12 @@
       <c r="C56">
         <v>53.491495</v>
       </c>
+      <c r="E56">
+        <v>0.72</v>
+      </c>
+      <c r="F56">
+        <v>53.37</v>
+      </c>
       <c r="I56">
         <v>0.72</v>
       </c>
@@ -17672,6 +20114,12 @@
       <c r="C57">
         <v>53.506562000000002</v>
       </c>
+      <c r="E57">
+        <v>0.73</v>
+      </c>
+      <c r="F57">
+        <v>53.39</v>
+      </c>
       <c r="I57">
         <v>0.73</v>
       </c>
@@ -17686,6 +20134,12 @@
       <c r="C58">
         <v>53.518298000000001</v>
       </c>
+      <c r="E58">
+        <v>0.74</v>
+      </c>
+      <c r="F58">
+        <v>53.4</v>
+      </c>
       <c r="I58">
         <v>0.74</v>
       </c>
@@ -17700,6 +20154,12 @@
       <c r="C59">
         <v>53.519356000000002</v>
       </c>
+      <c r="E59">
+        <v>0.75</v>
+      </c>
+      <c r="F59">
+        <v>53.41</v>
+      </c>
       <c r="I59">
         <v>0.75</v>
       </c>
@@ -17714,6 +20174,12 @@
       <c r="C60">
         <v>53.519047999999998</v>
       </c>
+      <c r="E60">
+        <v>0.76</v>
+      </c>
+      <c r="F60">
+        <v>53.42</v>
+      </c>
       <c r="I60">
         <v>0.76</v>
       </c>
@@ -17728,6 +20194,12 @@
       <c r="C61">
         <v>53.517434999999999</v>
       </c>
+      <c r="E61">
+        <v>0.77</v>
+      </c>
+      <c r="F61">
+        <v>53.43</v>
+      </c>
       <c r="I61">
         <v>0.77</v>
       </c>
@@ -17742,6 +20214,12 @@
       <c r="C62">
         <v>53.514597000000002</v>
       </c>
+      <c r="E62">
+        <v>0.78</v>
+      </c>
+      <c r="F62">
+        <v>53.43</v>
+      </c>
       <c r="I62">
         <v>0.78</v>
       </c>
@@ -17756,6 +20234,12 @@
       <c r="C63">
         <v>53.505654</v>
       </c>
+      <c r="E63">
+        <v>0.79</v>
+      </c>
+      <c r="F63">
+        <v>53.44</v>
+      </c>
       <c r="I63">
         <v>0.79</v>
       </c>
@@ -17770,6 +20254,12 @@
       <c r="C64">
         <v>53.499802000000003</v>
       </c>
+      <c r="E64">
+        <v>0.8</v>
+      </c>
+      <c r="F64">
+        <v>53.45</v>
+      </c>
       <c r="I64">
         <v>0.8</v>
       </c>
@@ -17784,6 +20274,12 @@
       <c r="C65">
         <v>53.493234999999999</v>
       </c>
+      <c r="E65">
+        <v>0.81</v>
+      </c>
+      <c r="F65">
+        <v>53.46</v>
+      </c>
       <c r="I65">
         <v>0.81</v>
       </c>
@@ -17798,6 +20294,12 @@
       <c r="C66">
         <v>53.486131999999998</v>
       </c>
+      <c r="E66">
+        <v>0.82</v>
+      </c>
+      <c r="F66">
+        <v>53.46</v>
+      </c>
       <c r="I66">
         <v>0.82</v>
       </c>
@@ -17812,6 +20314,12 @@
       <c r="C67">
         <v>53.478695000000002</v>
       </c>
+      <c r="E67">
+        <v>0.83</v>
+      </c>
+      <c r="F67">
+        <v>53.47</v>
+      </c>
       <c r="I67">
         <v>0.83</v>
       </c>
@@ -17826,6 +20334,12 @@
       <c r="C68">
         <v>53.471153000000001</v>
       </c>
+      <c r="E68">
+        <v>0.84</v>
+      </c>
+      <c r="F68">
+        <v>53.48</v>
+      </c>
       <c r="I68">
         <v>0.84</v>
       </c>
@@ -17840,6 +20354,12 @@
       <c r="C69">
         <v>53.463757000000001</v>
       </c>
+      <c r="E69">
+        <v>0.85</v>
+      </c>
+      <c r="F69">
+        <v>53.48</v>
+      </c>
       <c r="I69">
         <v>0.85</v>
       </c>
@@ -17854,6 +20374,12 @@
       <c r="C70">
         <v>53.456783000000001</v>
       </c>
+      <c r="E70">
+        <v>0.86</v>
+      </c>
+      <c r="F70">
+        <v>53.49</v>
+      </c>
       <c r="I70">
         <v>0.86</v>
       </c>
@@ -17868,6 +20394,12 @@
       <c r="C71">
         <v>53.450535000000002</v>
       </c>
+      <c r="E71">
+        <v>0.87</v>
+      </c>
+      <c r="F71">
+        <v>53.49</v>
+      </c>
       <c r="I71">
         <v>0.87</v>
       </c>
@@ -17882,6 +20414,12 @@
       <c r="C72">
         <v>53.445343999999999</v>
       </c>
+      <c r="E72">
+        <v>0.88</v>
+      </c>
+      <c r="F72">
+        <v>53.49</v>
+      </c>
       <c r="I72">
         <v>0.88</v>
       </c>
@@ -17896,6 +20434,12 @@
       <c r="C73">
         <v>53.441567999999997</v>
       </c>
+      <c r="E73">
+        <v>0.89</v>
+      </c>
+      <c r="F73">
+        <v>53.49</v>
+      </c>
       <c r="I73">
         <v>0.89</v>
       </c>
@@ -17904,6 +20448,12 @@
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E74">
+        <v>0.9</v>
+      </c>
+      <c r="F74">
+        <v>53.5</v>
+      </c>
       <c r="I74">
         <v>0.9</v>
       </c>
@@ -17912,6 +20462,12 @@
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E75">
+        <v>0.91</v>
+      </c>
+      <c r="F75">
+        <v>53.5</v>
+      </c>
       <c r="I75">
         <v>0.91</v>
       </c>
@@ -17920,6 +20476,12 @@
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E76">
+        <v>0.92</v>
+      </c>
+      <c r="F76">
+        <v>53.5</v>
+      </c>
       <c r="I76">
         <v>0.92</v>
       </c>
@@ -17928,6 +20490,12 @@
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E77">
+        <v>0.93</v>
+      </c>
+      <c r="F77">
+        <v>53.5</v>
+      </c>
       <c r="I77">
         <v>0.93</v>
       </c>
@@ -17936,6 +20504,12 @@
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E78">
+        <v>0.94</v>
+      </c>
+      <c r="F78">
+        <v>53.5</v>
+      </c>
       <c r="I78">
         <v>0.94</v>
       </c>
@@ -17944,6 +20518,12 @@
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E79">
+        <v>0.95</v>
+      </c>
+      <c r="F79">
+        <v>53.5</v>
+      </c>
       <c r="I79">
         <v>0.95</v>
       </c>
@@ -17952,6 +20532,12 @@
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="E80">
+        <v>0.96</v>
+      </c>
+      <c r="F80">
+        <v>53.49</v>
+      </c>
       <c r="I80">
         <v>0.96</v>
       </c>
@@ -17959,7 +20545,13 @@
         <v>53.53</v>
       </c>
     </row>
-    <row r="81" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E81">
+        <v>0.97</v>
+      </c>
+      <c r="F81">
+        <v>53.49</v>
+      </c>
       <c r="I81">
         <v>0.97</v>
       </c>
@@ -17967,7 +20559,13 @@
         <v>53.53</v>
       </c>
     </row>
-    <row r="82" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E82">
+        <v>0.98</v>
+      </c>
+      <c r="F82">
+        <v>53.49</v>
+      </c>
       <c r="I82">
         <v>0.98</v>
       </c>
@@ -17975,7 +20573,13 @@
         <v>53.54</v>
       </c>
     </row>
-    <row r="83" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E83">
+        <v>0.99</v>
+      </c>
+      <c r="F83">
+        <v>53.48</v>
+      </c>
       <c r="I83">
         <v>0.99</v>
       </c>
@@ -19856,6 +22460,9 @@
       <c r="B3" t="s">
         <v>6</v>
       </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
       <c r="H3" t="s">
         <v>4</v>
       </c>
@@ -19867,6 +22474,12 @@
       <c r="C4" s="1">
         <v>52.840454999999999</v>
       </c>
+      <c r="E4">
+        <v>0.2</v>
+      </c>
+      <c r="F4">
+        <v>53.03</v>
+      </c>
       <c r="H4">
         <v>0.2</v>
       </c>
@@ -19881,6 +22494,12 @@
       <c r="C5" s="1">
         <v>52.940829999999998</v>
       </c>
+      <c r="E5">
+        <v>0.21</v>
+      </c>
+      <c r="F5">
+        <v>53.04</v>
+      </c>
       <c r="H5">
         <v>0.21</v>
       </c>
@@ -19895,6 +22514,12 @@
       <c r="C6" s="1">
         <v>53.025526999999997</v>
       </c>
+      <c r="E6">
+        <v>0.22</v>
+      </c>
+      <c r="F6">
+        <v>53.05</v>
+      </c>
       <c r="H6">
         <v>0.22</v>
       </c>
@@ -19909,6 +22534,12 @@
       <c r="C7" s="1">
         <v>53.096209000000002</v>
       </c>
+      <c r="E7">
+        <v>0.23</v>
+      </c>
+      <c r="F7">
+        <v>53.06</v>
+      </c>
       <c r="H7">
         <v>0.23</v>
       </c>
@@ -19923,6 +22554,12 @@
       <c r="C8" s="1">
         <v>53.154434999999999</v>
       </c>
+      <c r="E8">
+        <v>0.24</v>
+      </c>
+      <c r="F8">
+        <v>53.07</v>
+      </c>
       <c r="H8">
         <v>0.24</v>
       </c>
@@ -19937,6 +22574,12 @@
       <c r="C9" s="1">
         <v>53.20167</v>
       </c>
+      <c r="E9">
+        <v>0.25</v>
+      </c>
+      <c r="F9">
+        <v>53.08</v>
+      </c>
       <c r="H9">
         <v>0.25</v>
       </c>
@@ -19951,6 +22594,12 @@
       <c r="C10" s="1">
         <v>53.239280999999998</v>
       </c>
+      <c r="E10">
+        <v>0.26</v>
+      </c>
+      <c r="F10">
+        <v>53.1</v>
+      </c>
       <c r="H10">
         <v>0.26</v>
       </c>
@@ -19965,6 +22614,12 @@
       <c r="C11" s="1">
         <v>53.268543999999999</v>
       </c>
+      <c r="E11">
+        <v>0.27</v>
+      </c>
+      <c r="F11">
+        <v>53.11</v>
+      </c>
       <c r="H11">
         <v>0.27</v>
       </c>
@@ -19979,6 +22634,12 @@
       <c r="C12" s="1">
         <v>53.290643000000003</v>
       </c>
+      <c r="E12">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="F12">
+        <v>53.12</v>
+      </c>
       <c r="H12">
         <v>0.28000000000000003</v>
       </c>
@@ -19993,6 +22654,12 @@
       <c r="C13" s="1">
         <v>53.306679000000003</v>
       </c>
+      <c r="E13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="F13">
+        <v>53.13</v>
+      </c>
       <c r="H13">
         <v>0.28999999999999998</v>
       </c>
@@ -20007,6 +22674,12 @@
       <c r="C14" s="1">
         <v>53.317664999999998</v>
       </c>
+      <c r="E14">
+        <v>0.3</v>
+      </c>
+      <c r="F14">
+        <v>53.14</v>
+      </c>
       <c r="H14">
         <v>0.3</v>
       </c>
@@ -20021,6 +22694,12 @@
       <c r="C15" s="1">
         <v>53.324536000000002</v>
       </c>
+      <c r="E15">
+        <v>0.31</v>
+      </c>
+      <c r="F15">
+        <v>53.16</v>
+      </c>
       <c r="H15">
         <v>0.31</v>
       </c>
@@ -20035,6 +22714,12 @@
       <c r="C16" s="1">
         <v>53.328145999999997</v>
       </c>
+      <c r="E16">
+        <v>0.32</v>
+      </c>
+      <c r="F16">
+        <v>53.17</v>
+      </c>
       <c r="H16">
         <v>0.32</v>
       </c>
@@ -20049,6 +22734,12 @@
       <c r="C17" s="1">
         <v>53.329275000000003</v>
       </c>
+      <c r="E17">
+        <v>0.33</v>
+      </c>
+      <c r="F17">
+        <v>53.18</v>
+      </c>
       <c r="H17">
         <v>0.33</v>
       </c>
@@ -20063,6 +22754,12 @@
       <c r="C18" s="1">
         <v>53.328628000000002</v>
       </c>
+      <c r="E18">
+        <v>0.34</v>
+      </c>
+      <c r="F18">
+        <v>53.19</v>
+      </c>
       <c r="H18">
         <v>0.34</v>
       </c>
@@ -20077,6 +22774,12 @@
       <c r="C19" s="1">
         <v>53.326842999999997</v>
       </c>
+      <c r="E19">
+        <v>0.35</v>
+      </c>
+      <c r="F19">
+        <v>53.21</v>
+      </c>
       <c r="H19">
         <v>0.35</v>
       </c>
@@ -20091,6 +22794,12 @@
       <c r="C20" s="1">
         <v>53.324486</v>
       </c>
+      <c r="E20">
+        <v>0.36</v>
+      </c>
+      <c r="F20">
+        <v>53.22</v>
+      </c>
       <c r="H20">
         <v>0.36</v>
       </c>
@@ -20105,6 +22814,12 @@
       <c r="C21" s="1">
         <v>53.322063999999997</v>
       </c>
+      <c r="E21">
+        <v>0.37</v>
+      </c>
+      <c r="F21">
+        <v>53.23</v>
+      </c>
       <c r="H21">
         <v>0.37</v>
       </c>
@@ -20119,6 +22834,12 @@
       <c r="C22" s="1">
         <v>53.320017</v>
       </c>
+      <c r="E22">
+        <v>0.38</v>
+      </c>
+      <c r="F22">
+        <v>53.24</v>
+      </c>
       <c r="H22">
         <v>0.38</v>
       </c>
@@ -20133,6 +22854,12 @@
       <c r="C23" s="1">
         <v>53.318728999999998</v>
       </c>
+      <c r="E23">
+        <v>0.39</v>
+      </c>
+      <c r="F23">
+        <v>53.26</v>
+      </c>
       <c r="H23">
         <v>0.39</v>
       </c>
@@ -20147,6 +22874,12 @@
       <c r="C24" s="1">
         <v>53.318525999999999</v>
       </c>
+      <c r="E24">
+        <v>0.4</v>
+      </c>
+      <c r="F24">
+        <v>53.27</v>
+      </c>
       <c r="H24">
         <v>0.4</v>
       </c>
@@ -20161,6 +22894,12 @@
       <c r="C25" s="1">
         <v>53.319682</v>
       </c>
+      <c r="E25">
+        <v>0.41</v>
+      </c>
+      <c r="F25">
+        <v>53.28</v>
+      </c>
       <c r="H25">
         <v>0.41</v>
       </c>
@@ -20175,6 +22914,12 @@
       <c r="C26" s="1">
         <v>53.322418999999996</v>
       </c>
+      <c r="E26">
+        <v>0.42</v>
+      </c>
+      <c r="F26">
+        <v>53.3</v>
+      </c>
       <c r="H26">
         <v>0.42</v>
       </c>
@@ -20189,6 +22934,12 @@
       <c r="C27" s="1">
         <v>53.326912</v>
       </c>
+      <c r="E27">
+        <v>0.43</v>
+      </c>
+      <c r="F27">
+        <v>53.31</v>
+      </c>
       <c r="H27">
         <v>0.43</v>
       </c>
@@ -20203,6 +22954,12 @@
       <c r="C28" s="1">
         <v>53.333291000000003</v>
       </c>
+      <c r="E28">
+        <v>0.44</v>
+      </c>
+      <c r="F28">
+        <v>53.33</v>
+      </c>
       <c r="H28">
         <v>0.44</v>
       </c>
@@ -20217,6 +22974,12 @@
       <c r="C29" s="1">
         <v>53.341641000000003</v>
       </c>
+      <c r="E29">
+        <v>0.45</v>
+      </c>
+      <c r="F29">
+        <v>53.34</v>
+      </c>
       <c r="H29">
         <v>0.45</v>
       </c>
@@ -20231,6 +22994,12 @@
       <c r="C30" s="1">
         <v>53.352010999999997</v>
       </c>
+      <c r="E30">
+        <v>0.46</v>
+      </c>
+      <c r="F30">
+        <v>53.35</v>
+      </c>
       <c r="H30">
         <v>0.46</v>
       </c>
@@ -20245,6 +23014,12 @@
       <c r="C31" s="1">
         <v>53.364410999999997</v>
       </c>
+      <c r="E31">
+        <v>0.47</v>
+      </c>
+      <c r="F31">
+        <v>53.37</v>
+      </c>
       <c r="H31">
         <v>0.47</v>
       </c>
@@ -20259,6 +23034,12 @@
       <c r="C32" s="1">
         <v>53.378816999999998</v>
       </c>
+      <c r="E32">
+        <v>0.48</v>
+      </c>
+      <c r="F32">
+        <v>53.38</v>
+      </c>
       <c r="H32">
         <v>0.48</v>
       </c>
@@ -20273,6 +23054,12 @@
       <c r="C33" s="1">
         <v>53.395173999999997</v>
       </c>
+      <c r="E33">
+        <v>0.49</v>
+      </c>
+      <c r="F33">
+        <v>53.4</v>
+      </c>
       <c r="H33">
         <v>0.49</v>
       </c>
@@ -20287,6 +23074,12 @@
       <c r="C34" s="1">
         <v>53.413398999999998</v>
       </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>53.41</v>
+      </c>
       <c r="H34">
         <v>0.5</v>
       </c>
@@ -20301,6 +23094,12 @@
       <c r="C35" s="1">
         <v>53.433382999999999</v>
       </c>
+      <c r="E35">
+        <v>0.51</v>
+      </c>
+      <c r="F35">
+        <v>53.43</v>
+      </c>
       <c r="H35">
         <v>0.51</v>
       </c>
@@ -20315,6 +23114,12 @@
       <c r="C36" s="1">
         <v>53.454993999999999</v>
       </c>
+      <c r="E36">
+        <v>0.52</v>
+      </c>
+      <c r="F36">
+        <v>53.44</v>
+      </c>
       <c r="H36">
         <v>0.52</v>
       </c>
@@ -20329,6 +23134,12 @@
       <c r="C37" s="1">
         <v>53.478079000000001</v>
       </c>
+      <c r="E37">
+        <v>0.53</v>
+      </c>
+      <c r="F37">
+        <v>53.46</v>
+      </c>
       <c r="H37">
         <v>0.53</v>
       </c>
@@ -20343,6 +23154,12 @@
       <c r="C38" s="1">
         <v>53.502468</v>
       </c>
+      <c r="E38">
+        <v>0.54</v>
+      </c>
+      <c r="F38">
+        <v>53.47</v>
+      </c>
       <c r="H38">
         <v>0.54</v>
       </c>
@@ -20357,6 +23174,12 @@
       <c r="C39" s="1">
         <v>53.527977999999997</v>
       </c>
+      <c r="E39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F39">
+        <v>53.49</v>
+      </c>
       <c r="H39">
         <v>0.55000000000000004</v>
       </c>
@@ -20371,6 +23194,12 @@
       <c r="C40" s="1">
         <v>53.554411999999999</v>
       </c>
+      <c r="E40">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="F40">
+        <v>53.51</v>
+      </c>
       <c r="H40">
         <v>0.56000000000000005</v>
       </c>
@@ -20385,6 +23214,12 @@
       <c r="C41" s="1">
         <v>53.581564</v>
       </c>
+      <c r="E41">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="F41">
+        <v>53.52</v>
+      </c>
       <c r="H41">
         <v>0.56999999999999995</v>
       </c>
@@ -20399,6 +23234,12 @@
       <c r="C42" s="1">
         <v>53.609223999999998</v>
       </c>
+      <c r="E42">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F42">
+        <v>53.54</v>
+      </c>
       <c r="H42">
         <v>0.57999999999999996</v>
       </c>
@@ -20413,6 +23254,12 @@
       <c r="C43" s="1">
         <v>53.637174999999999</v>
       </c>
+      <c r="E43">
+        <v>0.59</v>
+      </c>
+      <c r="F43">
+        <v>53.55</v>
+      </c>
       <c r="H43">
         <v>0.59</v>
       </c>
@@ -20427,6 +23274,12 @@
       <c r="C44" s="1">
         <v>53.665202999999998</v>
       </c>
+      <c r="E44">
+        <v>0.6</v>
+      </c>
+      <c r="F44">
+        <v>53.57</v>
+      </c>
       <c r="H44">
         <v>0.6</v>
       </c>
@@ -20441,6 +23294,12 @@
       <c r="C45" s="1">
         <v>53.693092999999998</v>
       </c>
+      <c r="E45">
+        <v>0.61</v>
+      </c>
+      <c r="F45">
+        <v>53.59</v>
+      </c>
       <c r="H45">
         <v>0.61</v>
       </c>
@@ -20455,6 +23314,12 @@
       <c r="C46" s="1">
         <v>53.720637000000004</v>
       </c>
+      <c r="E46">
+        <v>0.62</v>
+      </c>
+      <c r="F46">
+        <v>53.6</v>
+      </c>
       <c r="H46">
         <v>0.62</v>
       </c>
@@ -20469,6 +23334,12 @@
       <c r="C47" s="1">
         <v>53.747633</v>
       </c>
+      <c r="E47">
+        <v>0.63</v>
+      </c>
+      <c r="F47">
+        <v>53.62</v>
+      </c>
       <c r="H47">
         <v>0.63</v>
       </c>
@@ -20483,6 +23354,12 @@
       <c r="C48" s="1">
         <v>53.773890000000002</v>
       </c>
+      <c r="E48">
+        <v>0.64</v>
+      </c>
+      <c r="F48">
+        <v>53.64</v>
+      </c>
       <c r="H48">
         <v>0.64</v>
       </c>
@@ -20497,6 +23374,12 @@
       <c r="C49" s="1">
         <v>53.799230000000001</v>
       </c>
+      <c r="E49">
+        <v>0.65</v>
+      </c>
+      <c r="F49">
+        <v>53.66</v>
+      </c>
       <c r="H49">
         <v>0.65</v>
       </c>
@@ -20511,6 +23394,12 @@
       <c r="C50" s="1">
         <v>53.823492000000002</v>
       </c>
+      <c r="E50">
+        <v>0.66</v>
+      </c>
+      <c r="F50">
+        <v>53.67</v>
+      </c>
       <c r="H50">
         <v>0.66</v>
       </c>
@@ -20525,6 +23414,12 @@
       <c r="C51" s="1">
         <v>53.846532000000003</v>
       </c>
+      <c r="E51">
+        <v>0.67</v>
+      </c>
+      <c r="F51">
+        <v>53.69</v>
+      </c>
       <c r="H51">
         <v>0.67</v>
       </c>
@@ -20539,6 +23434,12 @@
       <c r="C52" s="1">
         <v>53.868228000000002</v>
       </c>
+      <c r="E52">
+        <v>0.68</v>
+      </c>
+      <c r="F52">
+        <v>53.71</v>
+      </c>
       <c r="H52">
         <v>0.68</v>
       </c>
@@ -20553,6 +23454,12 @@
       <c r="C53" s="1">
         <v>53.888483999999998</v>
       </c>
+      <c r="E53">
+        <v>0.69</v>
+      </c>
+      <c r="F53">
+        <v>53.73</v>
+      </c>
       <c r="H53">
         <v>0.69</v>
       </c>
@@ -20567,6 +23474,12 @@
       <c r="C54" s="1">
         <v>53.907228000000003</v>
       </c>
+      <c r="E54">
+        <v>0.7</v>
+      </c>
+      <c r="F54">
+        <v>53.74</v>
+      </c>
       <c r="H54">
         <v>0.7</v>
       </c>
@@ -20581,6 +23494,12 @@
       <c r="C55" s="1">
         <v>53.924419999999998</v>
       </c>
+      <c r="E55">
+        <v>0.71</v>
+      </c>
+      <c r="F55">
+        <v>53.76</v>
+      </c>
       <c r="H55">
         <v>0.71</v>
       </c>
@@ -20595,6 +23514,12 @@
       <c r="C56" s="1">
         <v>53.940052000000001</v>
       </c>
+      <c r="E56">
+        <v>0.72</v>
+      </c>
+      <c r="F56">
+        <v>53.78</v>
+      </c>
       <c r="H56">
         <v>0.72</v>
       </c>
@@ -20609,6 +23534,12 @@
       <c r="C57" s="1">
         <v>53.954152000000001</v>
       </c>
+      <c r="E57">
+        <v>0.73</v>
+      </c>
+      <c r="F57">
+        <v>53.8</v>
+      </c>
       <c r="H57">
         <v>0.73</v>
       </c>
@@ -20623,6 +23554,12 @@
       <c r="C58" s="1">
         <v>53.966785000000002</v>
       </c>
+      <c r="E58">
+        <v>0.74</v>
+      </c>
+      <c r="F58">
+        <v>53.82</v>
+      </c>
       <c r="H58">
         <v>0.74</v>
       </c>
@@ -20637,6 +23574,12 @@
       <c r="C59" s="1">
         <v>53.978057999999997</v>
       </c>
+      <c r="E59">
+        <v>0.75</v>
+      </c>
+      <c r="F59">
+        <v>53.84</v>
+      </c>
       <c r="H59">
         <v>0.75</v>
       </c>
@@ -20651,6 +23594,12 @@
       <c r="C60" s="1">
         <v>53.988121</v>
       </c>
+      <c r="E60">
+        <v>0.76</v>
+      </c>
+      <c r="F60">
+        <v>53.86</v>
+      </c>
       <c r="H60">
         <v>0.76</v>
       </c>
@@ -20665,6 +23614,12 @@
       <c r="C61" s="1">
         <v>53.997169999999997</v>
       </c>
+      <c r="E61">
+        <v>0.77</v>
+      </c>
+      <c r="F61">
+        <v>53.88</v>
+      </c>
       <c r="H61">
         <v>0.77</v>
       </c>
@@ -20679,6 +23634,12 @@
       <c r="C62" s="1">
         <v>54.005451000000001</v>
       </c>
+      <c r="E62">
+        <v>0.78</v>
+      </c>
+      <c r="F62">
+        <v>53.9</v>
+      </c>
       <c r="H62">
         <v>0.78</v>
       </c>
@@ -20693,6 +23654,12 @@
       <c r="C63" s="1">
         <v>54.013263000000002</v>
       </c>
+      <c r="E63">
+        <v>0.79</v>
+      </c>
+      <c r="F63">
+        <v>53.92</v>
+      </c>
       <c r="H63">
         <v>0.79</v>
       </c>
@@ -20707,6 +23674,12 @@
       <c r="C64" s="1">
         <v>54.020958999999998</v>
       </c>
+      <c r="E64">
+        <v>0.8</v>
+      </c>
+      <c r="F64">
+        <v>53.94</v>
+      </c>
       <c r="H64">
         <v>0.8</v>
       </c>
@@ -20721,6 +23694,12 @@
       <c r="C65" s="1">
         <v>54.028948</v>
       </c>
+      <c r="E65">
+        <v>0.81</v>
+      </c>
+      <c r="F65">
+        <v>53.96</v>
+      </c>
       <c r="H65">
         <v>0.81</v>
       </c>
@@ -20735,6 +23714,12 @@
       <c r="C66" s="1">
         <v>54.037702000000003</v>
       </c>
+      <c r="E66">
+        <v>0.82</v>
+      </c>
+      <c r="F66">
+        <v>53.98</v>
+      </c>
       <c r="H66">
         <v>0.82</v>
       </c>
@@ -20749,6 +23734,12 @@
       <c r="C67" s="1">
         <v>54.047755000000002</v>
       </c>
+      <c r="E67">
+        <v>0.83</v>
+      </c>
+      <c r="F67">
+        <v>54</v>
+      </c>
       <c r="H67">
         <v>0.83</v>
       </c>
@@ -20763,6 +23754,12 @@
       <c r="C68" s="1">
         <v>54.059707000000003</v>
       </c>
+      <c r="E68">
+        <v>0.84</v>
+      </c>
+      <c r="F68">
+        <v>54.02</v>
+      </c>
       <c r="H68">
         <v>0.84</v>
       </c>
@@ -20777,6 +23774,12 @@
       <c r="C69" s="1">
         <v>54.074226000000003</v>
       </c>
+      <c r="E69">
+        <v>0.85</v>
+      </c>
+      <c r="F69">
+        <v>54.04</v>
+      </c>
       <c r="H69">
         <v>0.85</v>
       </c>
@@ -20791,6 +23794,12 @@
       <c r="C70" s="1">
         <v>54.092052000000002</v>
       </c>
+      <c r="E70">
+        <v>0.86</v>
+      </c>
+      <c r="F70">
+        <v>54.06</v>
+      </c>
       <c r="H70">
         <v>0.86</v>
       </c>
@@ -20805,6 +23814,12 @@
       <c r="C71" s="1">
         <v>54.113999999999997</v>
       </c>
+      <c r="E71">
+        <v>0.87</v>
+      </c>
+      <c r="F71">
+        <v>54.09</v>
+      </c>
       <c r="H71">
         <v>0.87</v>
       </c>
@@ -20819,6 +23834,12 @@
       <c r="C72" s="1">
         <v>54.140962000000002</v>
       </c>
+      <c r="E72">
+        <v>0.88</v>
+      </c>
+      <c r="F72">
+        <v>54.11</v>
+      </c>
       <c r="H72">
         <v>0.88</v>
       </c>
@@ -20833,6 +23854,12 @@
       <c r="C73" s="1">
         <v>54.173909000000002</v>
       </c>
+      <c r="E73">
+        <v>0.89</v>
+      </c>
+      <c r="F73">
+        <v>54.13</v>
+      </c>
       <c r="H73">
         <v>0.89</v>
       </c>
@@ -20847,6 +23874,12 @@
       <c r="C74" s="1">
         <v>54.213894000000003</v>
       </c>
+      <c r="E74">
+        <v>0.9</v>
+      </c>
+      <c r="F74">
+        <v>54.15</v>
+      </c>
       <c r="H74">
         <v>0.9</v>
       </c>
@@ -20861,6 +23894,12 @@
       <c r="C75" s="1">
         <v>54.262056999999999</v>
       </c>
+      <c r="E75">
+        <v>0.91</v>
+      </c>
+      <c r="F75">
+        <v>54.17</v>
+      </c>
       <c r="H75">
         <v>0.91</v>
       </c>
@@ -20875,6 +23914,12 @@
       <c r="C76" s="1">
         <v>54.319626</v>
       </c>
+      <c r="E76">
+        <v>0.92</v>
+      </c>
+      <c r="F76">
+        <v>54.2</v>
+      </c>
       <c r="H76">
         <v>0.92</v>
       </c>
@@ -20889,6 +23934,12 @@
       <c r="C77" s="1">
         <v>54.387917999999999</v>
       </c>
+      <c r="E77">
+        <v>0.93</v>
+      </c>
+      <c r="F77">
+        <v>54.22</v>
+      </c>
       <c r="H77">
         <v>0.93</v>
       </c>
@@ -20903,6 +23954,12 @@
       <c r="C78" s="1">
         <v>54.468347000000001</v>
       </c>
+      <c r="E78">
+        <v>0.94</v>
+      </c>
+      <c r="F78">
+        <v>54.24</v>
+      </c>
       <c r="H78">
         <v>0.94</v>
       </c>
@@ -20917,6 +23974,12 @@
       <c r="C79" s="1">
         <v>54.562420000000003</v>
       </c>
+      <c r="E79">
+        <v>0.95</v>
+      </c>
+      <c r="F79">
+        <v>54.27</v>
+      </c>
       <c r="H79">
         <v>0.95</v>
       </c>
@@ -20925,6 +23988,12 @@
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E80">
+        <v>0.96</v>
+      </c>
+      <c r="F80">
+        <v>54.29</v>
+      </c>
       <c r="H80">
         <v>0.96</v>
       </c>
@@ -20932,7 +24001,13 @@
         <v>54.29</v>
       </c>
     </row>
-    <row r="81" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E81">
+        <v>0.97</v>
+      </c>
+      <c r="F81">
+        <v>54.32</v>
+      </c>
       <c r="H81">
         <v>0.97</v>
       </c>
@@ -20940,7 +24015,13 @@
         <v>54.32</v>
       </c>
     </row>
-    <row r="82" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E82">
+        <v>0.98</v>
+      </c>
+      <c r="F82">
+        <v>54.34</v>
+      </c>
       <c r="H82">
         <v>0.98</v>
       </c>
@@ -20948,7 +24029,13 @@
         <v>54.34</v>
       </c>
     </row>
-    <row r="83" spans="8:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="5:9" x14ac:dyDescent="0.3">
+      <c r="E83">
+        <v>0.99</v>
+      </c>
+      <c r="F83">
+        <v>54.36</v>
+      </c>
       <c r="H83">
         <v>0.99</v>
       </c>
@@ -22627,6 +25714,12 @@
       <c r="C4">
         <v>53.479058000000002</v>
       </c>
+      <c r="F4">
+        <v>0.2</v>
+      </c>
+      <c r="G4">
+        <v>53.31</v>
+      </c>
       <c r="J4">
         <v>0.2</v>
       </c>
@@ -22641,6 +25734,12 @@
       <c r="C5">
         <v>53.507500999999998</v>
       </c>
+      <c r="F5">
+        <v>0.21</v>
+      </c>
+      <c r="G5">
+        <v>53.32</v>
+      </c>
       <c r="J5">
         <v>0.21</v>
       </c>
@@ -22655,6 +25754,12 @@
       <c r="C6">
         <v>53.528981999999999</v>
       </c>
+      <c r="F6">
+        <v>0.22</v>
+      </c>
+      <c r="G6">
+        <v>53.33</v>
+      </c>
       <c r="J6">
         <v>0.22</v>
       </c>
@@ -22669,6 +25774,12 @@
       <c r="C7">
         <v>53.544590999999997</v>
       </c>
+      <c r="F7">
+        <v>0.23</v>
+      </c>
+      <c r="G7">
+        <v>53.35</v>
+      </c>
       <c r="J7">
         <v>0.23</v>
       </c>
@@ -22683,6 +25794,12 @@
       <c r="C8">
         <v>53.565866</v>
       </c>
+      <c r="F8">
+        <v>0.24</v>
+      </c>
+      <c r="G8">
+        <v>53.36</v>
+      </c>
       <c r="J8">
         <v>0.24</v>
       </c>
@@ -22697,6 +25814,12 @@
       <c r="C9">
         <v>53.567267000000001</v>
       </c>
+      <c r="F9">
+        <v>0.25</v>
+      </c>
+      <c r="G9">
+        <v>53.37</v>
+      </c>
       <c r="J9">
         <v>0.25</v>
       </c>
@@ -22711,6 +25834,12 @@
       <c r="C10">
         <v>53.567048</v>
       </c>
+      <c r="F10">
+        <v>0.26</v>
+      </c>
+      <c r="G10">
+        <v>53.39</v>
+      </c>
       <c r="J10">
         <v>0.26</v>
       </c>
@@ -22725,6 +25854,12 @@
       <c r="C11">
         <v>53.565835999999997</v>
       </c>
+      <c r="F11">
+        <v>0.27</v>
+      </c>
+      <c r="G11">
+        <v>53.4</v>
+      </c>
       <c r="J11">
         <v>0.27</v>
       </c>
@@ -22739,6 +25874,12 @@
       <c r="C12">
         <v>53.564191999999998</v>
       </c>
+      <c r="F12">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G12">
+        <v>53.41</v>
+      </c>
       <c r="J12">
         <v>0.28000000000000003</v>
       </c>
@@ -22753,6 +25894,12 @@
       <c r="C13">
         <v>53.562610999999997</v>
       </c>
+      <c r="F13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G13">
+        <v>53.42</v>
+      </c>
       <c r="J13">
         <v>0.28999999999999998</v>
       </c>
@@ -22767,6 +25914,12 @@
       <c r="C14">
         <v>53.561526000000001</v>
       </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
+      <c r="G14">
+        <v>53.44</v>
+      </c>
       <c r="J14">
         <v>0.3</v>
       </c>
@@ -22781,6 +25934,12 @@
       <c r="C15">
         <v>53.561312000000001</v>
       </c>
+      <c r="F15">
+        <v>0.31</v>
+      </c>
+      <c r="G15">
+        <v>53.45</v>
+      </c>
       <c r="J15">
         <v>0.31</v>
       </c>
@@ -22795,6 +25954,12 @@
       <c r="C16">
         <v>53.562286</v>
       </c>
+      <c r="F16">
+        <v>0.32</v>
+      </c>
+      <c r="G16">
+        <v>53.47</v>
+      </c>
       <c r="J16">
         <v>0.32</v>
       </c>
@@ -22809,6 +25974,12 @@
       <c r="C17">
         <v>53.564712</v>
       </c>
+      <c r="F17">
+        <v>0.33</v>
+      </c>
+      <c r="G17">
+        <v>53.48</v>
+      </c>
       <c r="J17">
         <v>0.33</v>
       </c>
@@ -22823,6 +25994,12 @@
       <c r="C18">
         <v>53.568803000000003</v>
       </c>
+      <c r="F18">
+        <v>0.34</v>
+      </c>
+      <c r="G18">
+        <v>53.49</v>
+      </c>
       <c r="J18">
         <v>0.34</v>
       </c>
@@ -22837,6 +26014,12 @@
       <c r="C19">
         <v>53.574722999999999</v>
       </c>
+      <c r="F19">
+        <v>0.35</v>
+      </c>
+      <c r="G19">
+        <v>53.51</v>
+      </c>
       <c r="J19">
         <v>0.35</v>
       </c>
@@ -22851,6 +26034,12 @@
       <c r="C20">
         <v>53.582593000000003</v>
       </c>
+      <c r="F20">
+        <v>0.36</v>
+      </c>
+      <c r="G20">
+        <v>53.52</v>
+      </c>
       <c r="J20">
         <v>0.36</v>
       </c>
@@ -22865,6 +26054,12 @@
       <c r="C21">
         <v>53.592488000000003</v>
       </c>
+      <c r="F21">
+        <v>0.37</v>
+      </c>
+      <c r="G21">
+        <v>53.53</v>
+      </c>
       <c r="J21">
         <v>0.37</v>
       </c>
@@ -22879,6 +26074,12 @@
       <c r="C22">
         <v>53.604447</v>
       </c>
+      <c r="F22">
+        <v>0.38</v>
+      </c>
+      <c r="G22">
+        <v>53.55</v>
+      </c>
       <c r="J22">
         <v>0.38</v>
       </c>
@@ -22893,6 +26094,12 @@
       <c r="C23">
         <v>53.618468</v>
       </c>
+      <c r="F23">
+        <v>0.39</v>
+      </c>
+      <c r="G23">
+        <v>53.56</v>
+      </c>
       <c r="J23">
         <v>0.39</v>
       </c>
@@ -22907,6 +26114,12 @@
       <c r="C24">
         <v>53.634518999999997</v>
       </c>
+      <c r="F24">
+        <v>0.4</v>
+      </c>
+      <c r="G24">
+        <v>53.58</v>
+      </c>
       <c r="J24">
         <v>0.4</v>
       </c>
@@ -22921,6 +26134,12 @@
       <c r="C25">
         <v>53.652532000000001</v>
       </c>
+      <c r="F25">
+        <v>0.41</v>
+      </c>
+      <c r="G25">
+        <v>53.59</v>
+      </c>
       <c r="J25">
         <v>0.41</v>
       </c>
@@ -22935,6 +26154,12 @@
       <c r="C26">
         <v>53.672415000000001</v>
       </c>
+      <c r="F26">
+        <v>0.42</v>
+      </c>
+      <c r="G26">
+        <v>53.61</v>
+      </c>
       <c r="J26">
         <v>0.42</v>
       </c>
@@ -22949,6 +26174,12 @@
       <c r="C27">
         <v>53.694046999999998</v>
       </c>
+      <c r="F27">
+        <v>0.43</v>
+      </c>
+      <c r="G27">
+        <v>53.62</v>
+      </c>
       <c r="J27">
         <v>0.43</v>
       </c>
@@ -22963,6 +26194,12 @@
       <c r="C28">
         <v>53.717283000000002</v>
       </c>
+      <c r="F28">
+        <v>0.44</v>
+      </c>
+      <c r="G28">
+        <v>53.64</v>
+      </c>
       <c r="J28">
         <v>0.44</v>
       </c>
@@ -22977,6 +26214,12 @@
       <c r="C29">
         <v>53.741962000000001</v>
       </c>
+      <c r="F29">
+        <v>0.45</v>
+      </c>
+      <c r="G29">
+        <v>53.65</v>
+      </c>
       <c r="J29">
         <v>0.45</v>
       </c>
@@ -22991,6 +26234,12 @@
       <c r="C30">
         <v>53.767901000000002</v>
       </c>
+      <c r="F30">
+        <v>0.46</v>
+      </c>
+      <c r="G30">
+        <v>53.66</v>
+      </c>
       <c r="J30">
         <v>0.46</v>
       </c>
@@ -23005,6 +26254,12 @@
       <c r="C31">
         <v>53.794905</v>
       </c>
+      <c r="F31">
+        <v>0.47</v>
+      </c>
+      <c r="G31">
+        <v>53.68</v>
+      </c>
       <c r="J31">
         <v>0.47</v>
       </c>
@@ -23019,6 +26274,12 @@
       <c r="C32">
         <v>53.822764999999997</v>
       </c>
+      <c r="F32">
+        <v>0.48</v>
+      </c>
+      <c r="G32">
+        <v>53.69</v>
+      </c>
       <c r="J32">
         <v>0.48</v>
       </c>
@@ -23033,6 +26294,12 @@
       <c r="C33">
         <v>53.851264999999998</v>
       </c>
+      <c r="F33">
+        <v>0.49</v>
+      </c>
+      <c r="G33">
+        <v>53.71</v>
+      </c>
       <c r="J33">
         <v>0.49</v>
       </c>
@@ -23047,6 +26314,12 @@
       <c r="C34">
         <v>53.880181</v>
       </c>
+      <c r="F34">
+        <v>0.5</v>
+      </c>
+      <c r="G34">
+        <v>53.73</v>
+      </c>
       <c r="J34">
         <v>0.5</v>
       </c>
@@ -23061,6 +26334,12 @@
       <c r="C35">
         <v>53.909286000000002</v>
       </c>
+      <c r="F35">
+        <v>0.51</v>
+      </c>
+      <c r="G35">
+        <v>53.74</v>
+      </c>
       <c r="J35">
         <v>0.51</v>
       </c>
@@ -23075,6 +26354,12 @@
       <c r="C36">
         <v>53.938350999999997</v>
       </c>
+      <c r="F36">
+        <v>0.52</v>
+      </c>
+      <c r="G36">
+        <v>53.76</v>
+      </c>
       <c r="J36">
         <v>0.52</v>
       </c>
@@ -23089,6 +26374,12 @@
       <c r="C37">
         <v>53.967151000000001</v>
       </c>
+      <c r="F37">
+        <v>0.53</v>
+      </c>
+      <c r="G37">
+        <v>53.77</v>
+      </c>
       <c r="J37">
         <v>0.53</v>
       </c>
@@ -23103,6 +26394,12 @@
       <c r="C38">
         <v>53.995465000000003</v>
       </c>
+      <c r="F38">
+        <v>0.54</v>
+      </c>
+      <c r="G38">
+        <v>53.79</v>
+      </c>
       <c r="J38">
         <v>0.54</v>
       </c>
@@ -23117,6 +26414,12 @@
       <c r="C39">
         <v>54.023077000000001</v>
       </c>
+      <c r="F39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G39">
+        <v>53.8</v>
+      </c>
       <c r="J39">
         <v>0.55000000000000004</v>
       </c>
@@ -23131,6 +26434,12 @@
       <c r="C40">
         <v>54.049785</v>
       </c>
+      <c r="F40">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G40">
+        <v>53.82</v>
+      </c>
       <c r="J40">
         <v>0.56000000000000005</v>
       </c>
@@ -23145,6 +26454,12 @@
       <c r="C41">
         <v>54.075398</v>
       </c>
+      <c r="F41">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G41">
+        <v>53.84</v>
+      </c>
       <c r="J41">
         <v>0.56999999999999995</v>
       </c>
@@ -23159,6 +26474,12 @@
       <c r="C42">
         <v>54.099741000000002</v>
       </c>
+      <c r="F42">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G42">
+        <v>53.85</v>
+      </c>
       <c r="J42">
         <v>0.57999999999999996</v>
       </c>
@@ -23173,6 +26494,12 @@
       <c r="C43">
         <v>54.122658000000001</v>
       </c>
+      <c r="F43">
+        <v>0.59</v>
+      </c>
+      <c r="G43">
+        <v>53.87</v>
+      </c>
       <c r="J43">
         <v>0.59</v>
       </c>
@@ -23187,6 +26514,12 @@
       <c r="C44">
         <v>54.144013999999999</v>
       </c>
+      <c r="F44">
+        <v>0.6</v>
+      </c>
+      <c r="G44">
+        <v>53.88</v>
+      </c>
       <c r="J44">
         <v>0.6</v>
       </c>
@@ -23201,6 +26534,12 @@
       <c r="C45">
         <v>54.163699000000001</v>
       </c>
+      <c r="F45">
+        <v>0.61</v>
+      </c>
+      <c r="G45">
+        <v>53.9</v>
+      </c>
       <c r="J45">
         <v>0.61</v>
       </c>
@@ -23215,6 +26554,12 @@
       <c r="C46">
         <v>54.181629000000001</v>
       </c>
+      <c r="F46">
+        <v>0.62</v>
+      </c>
+      <c r="G46">
+        <v>53.92</v>
+      </c>
       <c r="J46">
         <v>0.62</v>
       </c>
@@ -23229,6 +26574,12 @@
       <c r="C47">
         <v>54.197749999999999</v>
       </c>
+      <c r="F47">
+        <v>0.63</v>
+      </c>
+      <c r="G47">
+        <v>53.93</v>
+      </c>
       <c r="J47">
         <v>0.63</v>
       </c>
@@ -23243,6 +26594,12 @@
       <c r="C48">
         <v>54.212040000000002</v>
       </c>
+      <c r="F48">
+        <v>0.64</v>
+      </c>
+      <c r="G48">
+        <v>53.95</v>
+      </c>
       <c r="J48">
         <v>0.64</v>
       </c>
@@ -23257,6 +26614,12 @@
       <c r="C49">
         <v>54.224513999999999</v>
       </c>
+      <c r="F49">
+        <v>0.65</v>
+      </c>
+      <c r="G49">
+        <v>53.97</v>
+      </c>
       <c r="J49">
         <v>0.65</v>
       </c>
@@ -23271,6 +26634,12 @@
       <c r="C50">
         <v>54.235224000000002</v>
       </c>
+      <c r="F50">
+        <v>0.66</v>
+      </c>
+      <c r="G50">
+        <v>53.99</v>
+      </c>
       <c r="J50">
         <v>0.66</v>
       </c>
@@ -23285,6 +26654,12 @@
       <c r="C51">
         <v>54.244261999999999</v>
       </c>
+      <c r="F51">
+        <v>0.67</v>
+      </c>
+      <c r="G51">
+        <v>54</v>
+      </c>
       <c r="J51">
         <v>0.67</v>
       </c>
@@ -23299,6 +26674,12 @@
       <c r="C52">
         <v>54.257914999999997</v>
       </c>
+      <c r="F52">
+        <v>0.68</v>
+      </c>
+      <c r="G52">
+        <v>54.02</v>
+      </c>
       <c r="J52">
         <v>0.68</v>
       </c>
@@ -23313,6 +26694,12 @@
       <c r="C53">
         <v>54.262945000000002</v>
       </c>
+      <c r="F53">
+        <v>0.69</v>
+      </c>
+      <c r="G53">
+        <v>54.04</v>
+      </c>
       <c r="J53">
         <v>0.69</v>
       </c>
@@ -23327,6 +26714,12 @@
       <c r="C54">
         <v>54.267139999999998</v>
       </c>
+      <c r="F54">
+        <v>0.7</v>
+      </c>
+      <c r="G54">
+        <v>54.06</v>
+      </c>
       <c r="J54">
         <v>0.7</v>
       </c>
@@ -23341,6 +26734,12 @@
       <c r="C55">
         <v>54.270837</v>
       </c>
+      <c r="F55">
+        <v>0.71</v>
+      </c>
+      <c r="G55">
+        <v>54.07</v>
+      </c>
       <c r="J55">
         <v>0.71</v>
       </c>
@@ -23355,6 +26754,12 @@
       <c r="C56">
         <v>54.274433999999999</v>
       </c>
+      <c r="F56">
+        <v>0.72</v>
+      </c>
+      <c r="G56">
+        <v>54.09</v>
+      </c>
       <c r="J56">
         <v>0.72</v>
       </c>
@@ -23369,6 +26774,12 @@
       <c r="C57">
         <v>54.278387000000002</v>
       </c>
+      <c r="F57">
+        <v>0.73</v>
+      </c>
+      <c r="G57">
+        <v>54.11</v>
+      </c>
       <c r="J57">
         <v>0.73</v>
       </c>
@@ -23383,6 +26794,12 @@
       <c r="C58">
         <v>54.283217</v>
       </c>
+      <c r="F58">
+        <v>0.74</v>
+      </c>
+      <c r="G58">
+        <v>54.13</v>
+      </c>
       <c r="J58">
         <v>0.74</v>
       </c>
@@ -23397,6 +26814,12 @@
       <c r="C59">
         <v>54.289507999999998</v>
       </c>
+      <c r="F59">
+        <v>0.75</v>
+      </c>
+      <c r="G59">
+        <v>54.15</v>
+      </c>
       <c r="J59">
         <v>0.75</v>
       </c>
@@ -23411,6 +26834,12 @@
       <c r="C60">
         <v>54.297915000000003</v>
       </c>
+      <c r="F60">
+        <v>0.76</v>
+      </c>
+      <c r="G60">
+        <v>54.17</v>
+      </c>
       <c r="J60">
         <v>0.76</v>
       </c>
@@ -23425,6 +26854,12 @@
       <c r="C61">
         <v>54.309165</v>
       </c>
+      <c r="F61">
+        <v>0.77</v>
+      </c>
+      <c r="G61">
+        <v>54.18</v>
+      </c>
       <c r="J61">
         <v>0.77</v>
       </c>
@@ -23439,6 +26874,12 @@
       <c r="C62">
         <v>54.324057000000003</v>
       </c>
+      <c r="F62">
+        <v>0.78</v>
+      </c>
+      <c r="G62">
+        <v>54.2</v>
+      </c>
       <c r="J62">
         <v>0.78</v>
       </c>
@@ -23453,6 +26894,12 @@
       <c r="C63">
         <v>54.343468999999999</v>
       </c>
+      <c r="F63">
+        <v>0.79</v>
+      </c>
+      <c r="G63">
+        <v>54.22</v>
+      </c>
       <c r="J63">
         <v>0.79</v>
       </c>
@@ -23467,6 +26914,12 @@
       <c r="C64">
         <v>54.368358000000001</v>
       </c>
+      <c r="F64">
+        <v>0.8</v>
+      </c>
+      <c r="G64">
+        <v>54.24</v>
+      </c>
       <c r="J64">
         <v>0.8</v>
       </c>
@@ -23481,6 +26934,12 @@
       <c r="C65">
         <v>54.399763</v>
       </c>
+      <c r="F65">
+        <v>0.81</v>
+      </c>
+      <c r="G65">
+        <v>54.26</v>
+      </c>
       <c r="J65">
         <v>0.81</v>
       </c>
@@ -23495,6 +26954,12 @@
       <c r="C66">
         <v>54.438808999999999</v>
       </c>
+      <c r="F66">
+        <v>0.82</v>
+      </c>
+      <c r="G66">
+        <v>54.28</v>
+      </c>
       <c r="J66">
         <v>0.82</v>
       </c>
@@ -23509,6 +26974,12 @@
       <c r="C67">
         <v>54.486710000000002</v>
       </c>
+      <c r="F67">
+        <v>0.83</v>
+      </c>
+      <c r="G67">
+        <v>54.3</v>
+      </c>
       <c r="J67">
         <v>0.83</v>
       </c>
@@ -23523,6 +26994,12 @@
       <c r="C68">
         <v>54.544767999999998</v>
       </c>
+      <c r="F68">
+        <v>0.84</v>
+      </c>
+      <c r="G68">
+        <v>54.32</v>
+      </c>
       <c r="J68">
         <v>0.84</v>
       </c>
@@ -23537,6 +27014,12 @@
       <c r="C69">
         <v>54.614384000000001</v>
       </c>
+      <c r="F69">
+        <v>0.85</v>
+      </c>
+      <c r="G69">
+        <v>54.34</v>
+      </c>
       <c r="J69">
         <v>0.85</v>
       </c>
@@ -23551,6 +27034,12 @@
       <c r="C70">
         <v>54.697049</v>
       </c>
+      <c r="F70">
+        <v>0.86</v>
+      </c>
+      <c r="G70">
+        <v>54.36</v>
+      </c>
       <c r="J70">
         <v>0.86</v>
       </c>
@@ -23565,6 +27054,12 @@
       <c r="C71">
         <v>54.794358000000003</v>
       </c>
+      <c r="F71">
+        <v>0.87</v>
+      </c>
+      <c r="G71">
+        <v>54.38</v>
+      </c>
       <c r="J71">
         <v>0.87</v>
       </c>
@@ -23573,6 +27068,12 @@
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F72">
+        <v>0.88</v>
+      </c>
+      <c r="G72">
+        <v>54.4</v>
+      </c>
       <c r="J72">
         <v>0.88</v>
       </c>
@@ -23581,6 +27082,12 @@
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F73">
+        <v>0.89</v>
+      </c>
+      <c r="G73">
+        <v>54.42</v>
+      </c>
       <c r="J73">
         <v>0.89</v>
       </c>
@@ -23589,6 +27096,12 @@
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F74">
+        <v>0.9</v>
+      </c>
+      <c r="G74">
+        <v>54.44</v>
+      </c>
       <c r="J74">
         <v>0.9</v>
       </c>
@@ -23597,6 +27110,12 @@
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F75">
+        <v>0.91</v>
+      </c>
+      <c r="G75">
+        <v>54.46</v>
+      </c>
       <c r="J75">
         <v>0.91</v>
       </c>
@@ -23605,6 +27124,12 @@
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F76">
+        <v>0.92</v>
+      </c>
+      <c r="G76">
+        <v>54.48</v>
+      </c>
       <c r="J76">
         <v>0.92</v>
       </c>
@@ -23613,6 +27138,12 @@
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F77">
+        <v>0.93</v>
+      </c>
+      <c r="G77">
+        <v>54.5</v>
+      </c>
       <c r="J77">
         <v>0.93</v>
       </c>
@@ -23621,6 +27152,12 @@
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F78">
+        <v>0.94</v>
+      </c>
+      <c r="G78">
+        <v>54.52</v>
+      </c>
       <c r="J78">
         <v>0.94</v>
       </c>
@@ -23629,6 +27166,12 @@
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F79">
+        <v>0.95</v>
+      </c>
+      <c r="G79">
+        <v>54.54</v>
+      </c>
       <c r="J79">
         <v>0.95</v>
       </c>
@@ -23637,6 +27180,12 @@
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="F80">
+        <v>0.96</v>
+      </c>
+      <c r="G80">
+        <v>54.57</v>
+      </c>
       <c r="J80">
         <v>0.96</v>
       </c>
@@ -23644,7 +27193,13 @@
         <v>54.58</v>
       </c>
     </row>
-    <row r="81" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F81">
+        <v>0.97</v>
+      </c>
+      <c r="G81">
+        <v>54.59</v>
+      </c>
       <c r="J81">
         <v>0.97</v>
       </c>
@@ -23652,7 +27207,13 @@
         <v>54.6</v>
       </c>
     </row>
-    <row r="82" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F82">
+        <v>0.98</v>
+      </c>
+      <c r="G82">
+        <v>54.61</v>
+      </c>
       <c r="J82">
         <v>0.98</v>
       </c>
@@ -23660,7 +27221,13 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="83" spans="10:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="6:11" x14ac:dyDescent="0.3">
+      <c r="F83">
+        <v>0.99</v>
+      </c>
+      <c r="G83">
+        <v>54.63</v>
+      </c>
       <c r="J83">
         <v>0.99</v>
       </c>
@@ -25219,6 +28786,12 @@
       <c r="C4">
         <v>53.838906000000001</v>
       </c>
+      <c r="F4">
+        <v>0.2</v>
+      </c>
+      <c r="G4">
+        <v>53.52</v>
+      </c>
       <c r="I4">
         <v>0.2</v>
       </c>
@@ -25233,6 +28806,12 @@
       <c r="C5">
         <v>53.853166000000002</v>
       </c>
+      <c r="F5">
+        <v>0.21</v>
+      </c>
+      <c r="G5">
+        <v>53.54</v>
+      </c>
       <c r="I5">
         <v>0.21</v>
       </c>
@@ -25247,6 +28826,12 @@
       <c r="C6">
         <v>53.855905</v>
       </c>
+      <c r="F6">
+        <v>0.22</v>
+      </c>
+      <c r="G6">
+        <v>53.55</v>
+      </c>
       <c r="I6">
         <v>0.22</v>
       </c>
@@ -25261,6 +28846,12 @@
       <c r="C7">
         <v>53.856748000000003</v>
       </c>
+      <c r="F7">
+        <v>0.23</v>
+      </c>
+      <c r="G7">
+        <v>53.56</v>
+      </c>
       <c r="I7">
         <v>0.23</v>
       </c>
@@ -25275,6 +28866,12 @@
       <c r="C8">
         <v>53.856366999999999</v>
       </c>
+      <c r="F8">
+        <v>0.24</v>
+      </c>
+      <c r="G8">
+        <v>53.57</v>
+      </c>
       <c r="I8">
         <v>0.24</v>
       </c>
@@ -25289,6 +28886,12 @@
       <c r="C9">
         <v>53.854241000000002</v>
       </c>
+      <c r="F9">
+        <v>0.25</v>
+      </c>
+      <c r="G9">
+        <v>53.59</v>
+      </c>
       <c r="I9">
         <v>0.25</v>
       </c>
@@ -25303,6 +28906,12 @@
       <c r="C10">
         <v>53.853471999999996</v>
       </c>
+      <c r="F10">
+        <v>0.26</v>
+      </c>
+      <c r="G10">
+        <v>53.6</v>
+      </c>
       <c r="I10">
         <v>0.26</v>
       </c>
@@ -25317,6 +28926,12 @@
       <c r="C11">
         <v>53.853437</v>
       </c>
+      <c r="F11">
+        <v>0.27</v>
+      </c>
+      <c r="G11">
+        <v>53.61</v>
+      </c>
       <c r="I11">
         <v>0.27</v>
       </c>
@@ -25331,6 +28946,12 @@
       <c r="C12">
         <v>53.854458999999999</v>
       </c>
+      <c r="F12">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G12">
+        <v>53.63</v>
+      </c>
       <c r="I12">
         <v>0.28000000000000003</v>
       </c>
@@ -25345,6 +28966,12 @@
       <c r="C13">
         <v>53.856802999999999</v>
       </c>
+      <c r="F13">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G13">
+        <v>53.64</v>
+      </c>
       <c r="I13">
         <v>0.28999999999999998</v>
       </c>
@@ -25359,6 +28986,12 @@
       <c r="C14">
         <v>53.860677000000003</v>
       </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
+      <c r="G14">
+        <v>53.65</v>
+      </c>
       <c r="I14">
         <v>0.3</v>
       </c>
@@ -25373,6 +29006,12 @@
       <c r="C15">
         <v>53.866238000000003</v>
       </c>
+      <c r="F15">
+        <v>0.31</v>
+      </c>
+      <c r="G15">
+        <v>53.67</v>
+      </c>
       <c r="I15">
         <v>0.31</v>
       </c>
@@ -25387,6 +29026,12 @@
       <c r="C16">
         <v>53.87359</v>
       </c>
+      <c r="F16">
+        <v>0.32</v>
+      </c>
+      <c r="G16">
+        <v>53.68</v>
+      </c>
       <c r="I16">
         <v>0.32</v>
       </c>
@@ -25401,6 +29046,12 @@
       <c r="C17">
         <v>53.882796999999997</v>
       </c>
+      <c r="F17">
+        <v>0.33</v>
+      </c>
+      <c r="G17">
+        <v>53.69</v>
+      </c>
       <c r="I17">
         <v>0.33</v>
       </c>
@@ -25415,6 +29066,12 @@
       <c r="C18">
         <v>53.893875000000001</v>
       </c>
+      <c r="F18">
+        <v>0.34</v>
+      </c>
+      <c r="G18">
+        <v>53.71</v>
+      </c>
       <c r="I18">
         <v>0.34</v>
       </c>
@@ -25429,6 +29086,12 @@
       <c r="C19">
         <v>53.906806000000003</v>
       </c>
+      <c r="F19">
+        <v>0.35</v>
+      </c>
+      <c r="G19">
+        <v>53.72</v>
+      </c>
       <c r="I19">
         <v>0.35</v>
       </c>
@@ -25443,6 +29106,12 @@
       <c r="C20">
         <v>53.921531999999999</v>
       </c>
+      <c r="F20">
+        <v>0.36</v>
+      </c>
+      <c r="G20">
+        <v>53.73</v>
+      </c>
       <c r="I20">
         <v>0.36</v>
       </c>
@@ -25457,6 +29126,12 @@
       <c r="C21">
         <v>53.937967</v>
       </c>
+      <c r="F21">
+        <v>0.37</v>
+      </c>
+      <c r="G21">
+        <v>53.75</v>
+      </c>
       <c r="I21">
         <v>0.37</v>
       </c>
@@ -25471,6 +29146,12 @@
       <c r="C22">
         <v>53.955993999999997</v>
       </c>
+      <c r="F22">
+        <v>0.38</v>
+      </c>
+      <c r="G22">
+        <v>53.76</v>
+      </c>
       <c r="I22">
         <v>0.38</v>
       </c>
@@ -25485,6 +29166,12 @@
       <c r="C23">
         <v>53.975470000000001</v>
       </c>
+      <c r="F23">
+        <v>0.39</v>
+      </c>
+      <c r="G23">
+        <v>53.78</v>
+      </c>
       <c r="I23">
         <v>0.39</v>
       </c>
@@ -25499,6 +29186,12 @@
       <c r="C24">
         <v>53.996234000000001</v>
       </c>
+      <c r="F24">
+        <v>0.4</v>
+      </c>
+      <c r="G24">
+        <v>53.79</v>
+      </c>
       <c r="I24">
         <v>0.4</v>
       </c>
@@ -25513,6 +29206,12 @@
       <c r="C25">
         <v>54.018101999999999</v>
       </c>
+      <c r="F25">
+        <v>0.41</v>
+      </c>
+      <c r="G25">
+        <v>53.8</v>
+      </c>
       <c r="I25">
         <v>0.41</v>
       </c>
@@ -25527,6 +29226,12 @@
       <c r="C26">
         <v>54.040878999999997</v>
       </c>
+      <c r="F26">
+        <v>0.42</v>
+      </c>
+      <c r="G26">
+        <v>53.82</v>
+      </c>
       <c r="I26">
         <v>0.42</v>
       </c>
@@ -25541,6 +29246,12 @@
       <c r="C27">
         <v>54.064355999999997</v>
       </c>
+      <c r="F27">
+        <v>0.43</v>
+      </c>
+      <c r="G27">
+        <v>53.83</v>
+      </c>
       <c r="I27">
         <v>0.43</v>
       </c>
@@ -25555,6 +29266,12 @@
       <c r="C28">
         <v>54.088317000000004</v>
       </c>
+      <c r="F28">
+        <v>0.44</v>
+      </c>
+      <c r="G28">
+        <v>53.85</v>
+      </c>
       <c r="I28">
         <v>0.44</v>
       </c>
@@ -25569,6 +29286,12 @@
       <c r="C29">
         <v>54.112541</v>
       </c>
+      <c r="F29">
+        <v>0.45</v>
+      </c>
+      <c r="G29">
+        <v>53.86</v>
+      </c>
       <c r="I29">
         <v>0.45</v>
       </c>
@@ -25583,6 +29306,12 @@
       <c r="C30">
         <v>54.136805000000003</v>
       </c>
+      <c r="F30">
+        <v>0.46</v>
+      </c>
+      <c r="G30">
+        <v>53.88</v>
+      </c>
       <c r="I30">
         <v>0.46</v>
       </c>
@@ -25597,6 +29326,12 @@
       <c r="C31">
         <v>54.160890000000002</v>
       </c>
+      <c r="F31">
+        <v>0.47</v>
+      </c>
+      <c r="G31">
+        <v>53.89</v>
+      </c>
       <c r="I31">
         <v>0.47</v>
       </c>
@@ -25611,6 +29346,12 @@
       <c r="C32">
         <v>54.184581000000001</v>
       </c>
+      <c r="F32">
+        <v>0.48</v>
+      </c>
+      <c r="G32">
+        <v>53.91</v>
+      </c>
       <c r="I32">
         <v>0.48</v>
       </c>
@@ -25625,6 +29366,12 @@
       <c r="C33">
         <v>54.207672000000002</v>
       </c>
+      <c r="F33">
+        <v>0.49</v>
+      </c>
+      <c r="G33">
+        <v>53.92</v>
+      </c>
       <c r="I33">
         <v>0.49</v>
       </c>
@@ -25639,6 +29386,12 @@
       <c r="C34">
         <v>54.229970999999999</v>
       </c>
+      <c r="F34">
+        <v>0.5</v>
+      </c>
+      <c r="G34">
+        <v>53.94</v>
+      </c>
       <c r="I34">
         <v>0.5</v>
       </c>
@@ -25653,6 +29406,12 @@
       <c r="C35">
         <v>54.251300999999998</v>
       </c>
+      <c r="F35">
+        <v>0.51</v>
+      </c>
+      <c r="G35">
+        <v>53.95</v>
+      </c>
       <c r="I35">
         <v>0.51</v>
       </c>
@@ -25667,6 +29426,12 @@
       <c r="C36">
         <v>54.271504</v>
       </c>
+      <c r="F36">
+        <v>0.52</v>
+      </c>
+      <c r="G36">
+        <v>53.97</v>
+      </c>
       <c r="I36">
         <v>0.52</v>
       </c>
@@ -25681,6 +29446,12 @@
       <c r="C37">
         <v>54.290444000000001</v>
       </c>
+      <c r="F37">
+        <v>0.53</v>
+      </c>
+      <c r="G37">
+        <v>53.98</v>
+      </c>
       <c r="I37">
         <v>0.53</v>
       </c>
@@ -25695,6 +29466,12 @@
       <c r="C38">
         <v>54.308011999999998</v>
       </c>
+      <c r="F38">
+        <v>0.54</v>
+      </c>
+      <c r="G38">
+        <v>54</v>
+      </c>
       <c r="I38">
         <v>0.54</v>
       </c>
@@ -25709,6 +29486,12 @@
       <c r="C39">
         <v>54.324129999999997</v>
       </c>
+      <c r="F39">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G39">
+        <v>54.01</v>
+      </c>
       <c r="I39">
         <v>0.55000000000000004</v>
       </c>
@@ -25723,6 +29506,12 @@
       <c r="C40">
         <v>54.338749999999997</v>
       </c>
+      <c r="F40">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="G40">
+        <v>54.03</v>
+      </c>
       <c r="I40">
         <v>0.56000000000000005</v>
       </c>
@@ -25737,6 +29526,12 @@
       <c r="C41">
         <v>54.351863000000002</v>
       </c>
+      <c r="F41">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G41">
+        <v>54.04</v>
+      </c>
       <c r="I41">
         <v>0.56999999999999995</v>
       </c>
@@ -25751,6 +29546,12 @@
       <c r="C42">
         <v>54.363498999999997</v>
       </c>
+      <c r="F42">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G42">
+        <v>54.06</v>
+      </c>
       <c r="I42">
         <v>0.57999999999999996</v>
       </c>
@@ -25765,6 +29566,12 @@
       <c r="C43">
         <v>54.373730000000002</v>
       </c>
+      <c r="F43">
+        <v>0.59</v>
+      </c>
+      <c r="G43">
+        <v>54.07</v>
+      </c>
       <c r="I43">
         <v>0.59</v>
       </c>
@@ -25779,6 +29586,12 @@
       <c r="C44">
         <v>54.382674999999999</v>
       </c>
+      <c r="F44">
+        <v>0.6</v>
+      </c>
+      <c r="G44">
+        <v>54.09</v>
+      </c>
       <c r="I44">
         <v>0.6</v>
       </c>
@@ -25793,6 +29606,12 @@
       <c r="C45">
         <v>54.390504999999997</v>
       </c>
+      <c r="F45">
+        <v>0.61</v>
+      </c>
+      <c r="G45">
+        <v>54.11</v>
+      </c>
       <c r="I45">
         <v>0.61</v>
       </c>
@@ -25807,6 +29626,12 @@
       <c r="C46">
         <v>54.397444</v>
       </c>
+      <c r="F46">
+        <v>0.62</v>
+      </c>
+      <c r="G46">
+        <v>54.12</v>
+      </c>
       <c r="I46">
         <v>0.62</v>
       </c>
@@ -25821,6 +29646,12 @@
       <c r="C47">
         <v>54.403770000000002</v>
       </c>
+      <c r="F47">
+        <v>0.63</v>
+      </c>
+      <c r="G47">
+        <v>54.14</v>
+      </c>
       <c r="I47">
         <v>0.63</v>
       </c>
@@ -25835,6 +29666,12 @@
       <c r="C48">
         <v>54.409824999999998</v>
       </c>
+      <c r="F48">
+        <v>0.64</v>
+      </c>
+      <c r="G48">
+        <v>54.15</v>
+      </c>
       <c r="I48">
         <v>0.64</v>
       </c>
@@ -25849,6 +29686,12 @@
       <c r="C49">
         <v>54.416013</v>
       </c>
+      <c r="F49">
+        <v>0.65</v>
+      </c>
+      <c r="G49">
+        <v>54.17</v>
+      </c>
       <c r="I49">
         <v>0.65</v>
       </c>
@@ -25863,6 +29706,12 @@
       <c r="C50">
         <v>54.422804999999997</v>
       </c>
+      <c r="F50">
+        <v>0.66</v>
+      </c>
+      <c r="G50">
+        <v>54.19</v>
+      </c>
       <c r="I50">
         <v>0.66</v>
       </c>
@@ -25877,6 +29726,12 @@
       <c r="C51">
         <v>54.430743999999997</v>
       </c>
+      <c r="F51">
+        <v>0.67</v>
+      </c>
+      <c r="G51">
+        <v>54.2</v>
+      </c>
       <c r="I51">
         <v>0.67</v>
       </c>
@@ -25891,6 +29746,12 @@
       <c r="C52">
         <v>54.440444999999997</v>
       </c>
+      <c r="F52">
+        <v>0.68</v>
+      </c>
+      <c r="G52">
+        <v>54.22</v>
+      </c>
       <c r="I52">
         <v>0.68</v>
       </c>
@@ -25905,6 +29766,12 @@
       <c r="C53">
         <v>54.452603000000003</v>
       </c>
+      <c r="F53">
+        <v>0.69</v>
+      </c>
+      <c r="G53">
+        <v>54.24</v>
+      </c>
       <c r="I53">
         <v>0.69</v>
       </c>
@@ -25919,6 +29786,12 @@
       <c r="C54">
         <v>54.467992000000002</v>
       </c>
+      <c r="F54">
+        <v>0.7</v>
+      </c>
+      <c r="G54">
+        <v>54.25</v>
+      </c>
       <c r="I54">
         <v>0.7</v>
       </c>
@@ -25933,6 +29806,12 @@
       <c r="C55">
         <v>54.487470000000002</v>
       </c>
+      <c r="F55">
+        <v>0.71</v>
+      </c>
+      <c r="G55">
+        <v>54.27</v>
+      </c>
       <c r="I55">
         <v>0.71</v>
       </c>
@@ -25947,6 +29826,12 @@
       <c r="C56">
         <v>54.511983999999998</v>
       </c>
+      <c r="F56">
+        <v>0.72</v>
+      </c>
+      <c r="G56">
+        <v>54.29</v>
+      </c>
       <c r="I56">
         <v>0.72</v>
       </c>
@@ -25961,6 +29846,12 @@
       <c r="C57">
         <v>54.542571000000002</v>
       </c>
+      <c r="F57">
+        <v>0.73</v>
+      </c>
+      <c r="G57">
+        <v>54.31</v>
+      </c>
       <c r="I57">
         <v>0.73</v>
       </c>
@@ -25975,6 +29866,12 @@
       <c r="C58">
         <v>54.580365</v>
       </c>
+      <c r="F58">
+        <v>0.74</v>
+      </c>
+      <c r="G58">
+        <v>54.32</v>
+      </c>
       <c r="I58">
         <v>0.74</v>
       </c>
@@ -25989,6 +29886,12 @@
       <c r="C59">
         <v>54.626595000000002</v>
       </c>
+      <c r="F59">
+        <v>0.75</v>
+      </c>
+      <c r="G59">
+        <v>54.34</v>
+      </c>
       <c r="I59">
         <v>0.75</v>
       </c>
@@ -26003,6 +29906,12 @@
       <c r="C60">
         <v>54.682592999999997</v>
       </c>
+      <c r="F60">
+        <v>0.76</v>
+      </c>
+      <c r="G60">
+        <v>54.36</v>
+      </c>
       <c r="I60">
         <v>0.76</v>
       </c>
@@ -26017,6 +29926,12 @@
       <c r="C61">
         <v>54.749796000000003</v>
       </c>
+      <c r="F61">
+        <v>0.77</v>
+      </c>
+      <c r="G61">
+        <v>54.37</v>
+      </c>
       <c r="I61">
         <v>0.77</v>
       </c>
@@ -26031,6 +29946,12 @@
       <c r="C62">
         <v>54.829746999999998</v>
       </c>
+      <c r="F62">
+        <v>0.78</v>
+      </c>
+      <c r="G62">
+        <v>54.39</v>
+      </c>
       <c r="I62">
         <v>0.78</v>
       </c>
@@ -26045,6 +29966,12 @@
       <c r="C63">
         <v>54.924104</v>
       </c>
+      <c r="F63">
+        <v>0.79</v>
+      </c>
+      <c r="G63">
+        <v>54.41</v>
+      </c>
       <c r="I63">
         <v>0.79</v>
       </c>
@@ -26059,6 +29986,12 @@
       <c r="C64">
         <v>55.034638000000001</v>
       </c>
+      <c r="F64">
+        <v>0.8</v>
+      </c>
+      <c r="G64">
+        <v>54.43</v>
+      </c>
       <c r="I64">
         <v>0.8</v>
       </c>
@@ -26066,7 +29999,13 @@
         <v>54.41</v>
       </c>
     </row>
-    <row r="65" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F65">
+        <v>0.81</v>
+      </c>
+      <c r="G65">
+        <v>54.45</v>
+      </c>
       <c r="I65">
         <v>0.81</v>
       </c>
@@ -26074,7 +30013,13 @@
         <v>54.43</v>
       </c>
     </row>
-    <row r="66" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F66">
+        <v>0.82</v>
+      </c>
+      <c r="G66">
+        <v>54.46</v>
+      </c>
       <c r="I66">
         <v>0.82</v>
       </c>
@@ -26082,7 +30027,13 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="67" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F67">
+        <v>0.83</v>
+      </c>
+      <c r="G67">
+        <v>54.48</v>
+      </c>
       <c r="I67">
         <v>0.83</v>
       </c>
@@ -26090,7 +30041,13 @@
         <v>54.47</v>
       </c>
     </row>
-    <row r="68" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F68">
+        <v>0.84</v>
+      </c>
+      <c r="G68">
+        <v>54.5</v>
+      </c>
       <c r="I68">
         <v>0.84</v>
       </c>
@@ -26098,7 +30055,13 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="69" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F69">
+        <v>0.85</v>
+      </c>
+      <c r="G69">
+        <v>54.52</v>
+      </c>
       <c r="I69">
         <v>0.85</v>
       </c>
@@ -26106,7 +30069,13 @@
         <v>54.52</v>
       </c>
     </row>
-    <row r="70" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F70">
+        <v>0.86</v>
+      </c>
+      <c r="G70">
+        <v>54.54</v>
+      </c>
       <c r="I70">
         <v>0.86</v>
       </c>
@@ -26114,7 +30083,13 @@
         <v>54.54</v>
       </c>
     </row>
-    <row r="71" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F71">
+        <v>0.87</v>
+      </c>
+      <c r="G71">
+        <v>54.56</v>
+      </c>
       <c r="I71">
         <v>0.87</v>
       </c>
@@ -26122,7 +30097,13 @@
         <v>54.56</v>
       </c>
     </row>
-    <row r="72" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F72">
+        <v>0.88</v>
+      </c>
+      <c r="G72">
+        <v>54.58</v>
+      </c>
       <c r="I72">
         <v>0.88</v>
       </c>
@@ -26130,7 +30111,13 @@
         <v>54.59</v>
       </c>
     </row>
-    <row r="73" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F73">
+        <v>0.89</v>
+      </c>
+      <c r="G73">
+        <v>54.59</v>
+      </c>
       <c r="I73">
         <v>0.89</v>
       </c>
@@ -26138,7 +30125,13 @@
         <v>54.61</v>
       </c>
     </row>
-    <row r="74" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F74">
+        <v>0.9</v>
+      </c>
+      <c r="G74">
+        <v>54.61</v>
+      </c>
       <c r="I74">
         <v>0.9</v>
       </c>
@@ -26146,7 +30139,13 @@
         <v>54.64</v>
       </c>
     </row>
-    <row r="75" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F75">
+        <v>0.91</v>
+      </c>
+      <c r="G75">
+        <v>54.63</v>
+      </c>
       <c r="I75">
         <v>0.91</v>
       </c>
@@ -26154,7 +30153,13 @@
         <v>54.66</v>
       </c>
     </row>
-    <row r="76" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F76">
+        <v>0.92</v>
+      </c>
+      <c r="G76">
+        <v>54.65</v>
+      </c>
       <c r="I76">
         <v>0.92</v>
       </c>
@@ -26162,7 +30167,13 @@
         <v>54.68</v>
       </c>
     </row>
-    <row r="77" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F77">
+        <v>0.93</v>
+      </c>
+      <c r="G77">
+        <v>54.67</v>
+      </c>
       <c r="I77">
         <v>0.93</v>
       </c>
@@ -26170,7 +30181,13 @@
         <v>54.71</v>
       </c>
     </row>
-    <row r="78" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F78">
+        <v>0.94</v>
+      </c>
+      <c r="G78">
+        <v>54.69</v>
+      </c>
       <c r="I78">
         <v>0.94</v>
       </c>
@@ -26178,7 +30195,13 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="79" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F79">
+        <v>0.95</v>
+      </c>
+      <c r="G79">
+        <v>54.71</v>
+      </c>
       <c r="I79">
         <v>0.95</v>
       </c>
@@ -26186,7 +30209,13 @@
         <v>54.76</v>
       </c>
     </row>
-    <row r="80" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F80">
+        <v>0.96</v>
+      </c>
+      <c r="G80">
+        <v>54.73</v>
+      </c>
       <c r="I80">
         <v>0.96</v>
       </c>
@@ -26194,7 +30223,13 @@
         <v>54.79</v>
       </c>
     </row>
-    <row r="81" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F81">
+        <v>0.97</v>
+      </c>
+      <c r="G81">
+        <v>54.75</v>
+      </c>
       <c r="I81">
         <v>0.97</v>
       </c>
@@ -26202,7 +30237,13 @@
         <v>54.81</v>
       </c>
     </row>
-    <row r="82" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F82">
+        <v>0.98</v>
+      </c>
+      <c r="G82">
+        <v>54.77</v>
+      </c>
       <c r="I82">
         <v>0.98</v>
       </c>
@@ -26210,7 +30251,13 @@
         <v>54.84</v>
       </c>
     </row>
-    <row r="83" spans="9:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="6:10" x14ac:dyDescent="0.3">
+      <c r="F83">
+        <v>0.99</v>
+      </c>
+      <c r="G83">
+        <v>54.79</v>
+      </c>
       <c r="I83">
         <v>0.99</v>
       </c>
